--- a/client/DataCleaner/generated/Fastag_Cleaned.xlsx
+++ b/client/DataCleaner/generated/Fastag_Cleaned.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,9 +33,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,12 +67,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -443,14 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -486,156 +480,6 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HR55AX8283</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>28-03-2026 20:14:19</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>5366472728032620141969/5438625742</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Trip (RRN No / Trip No)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Plaza Name:Bijwasan- Lane ID:27</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HR55AX8283</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>27-03-2026 19:31:09</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>5366472827032619310921/5435290692</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Trip (RRN No / Trip No)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Plaza Name:Bijwasan- Lane ID:28</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HR55AX8283</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>27-03-2026 16:41:31</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5366471027032616413141/5434795127</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Trip (RRN No / Trip No)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Plaza Name:Bijwasan- Lane ID:10</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HR55AX8283</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>27-03-2026 10:20:20</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5366472327032610202035/5433820989</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Trip (RRN No / Trip No)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Plaza Name:Bijwasan- Lane ID:23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HR55AX8283</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>27-03-2026 09:21:49</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5366470627032609214958/5433666837</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Trip (RRN No / Trip No)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Plaza Name:Bijwasan- Lane ID:6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>220</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/client/DataCleaner/generated/Fastag_Cleaned.xlsx
+++ b/client/DataCleaner/generated/Fastag_Cleaned.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,9 +70,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,14 +443,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -480,6 +486,186 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ER030426</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>31-03-2026 12:03:57</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>_53664709310326120357095446538148</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Toll Payment</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bijwasan- Lane ID:9</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ER030426</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>31-03-2026 12:01:17</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>_PKT000000309592494</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Toll Payment</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Payment through Bharat Bill Pay</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ER030426</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:46:29</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>_53664715100326104629585382615809</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Toll Payment</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Bijwasan- Lane ID:15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ER030426</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>10-03-2026 10:31:10</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>_00700102210032610311005382575013</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Toll Payment</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ManesarTollPlaza- Lane ID:22</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ER030426</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:39:49</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>_53664731090326083949735379414292</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Toll Payment</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Bijwasan- Lane ID:31</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ER030426</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:17:50</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>_PKT000000306268161</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Toll Payment</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Payment through Bharat Bill Pay</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
